--- a/output/科研训练计划_2025-2026-2/06_达成度报告分析底表.xlsx
+++ b/output/科研训练计划_2025-2026-2/06_达成度报告分析底表.xlsx
@@ -568,7 +568,7 @@
         <v>0.8368277482142856</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>课程目标1综合平均达成值为0.837，达到预设达标阈值0.70。低分段占比为1.2%，高分段占比为87.5%。</t>
+          <t>课程目标1综合平均达成值为0.837，达到预设达标阈值0.60。低分段占比为1.2%，高分段占比为87.5%。</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -650,7 +650,7 @@
         <v>0.8333325729166667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>课程目标2综合平均达成值为0.833，达到预设达标阈值0.70。低分段占比为0.0%，高分段占比为66.2%。</t>
+          <t>课程目标2综合平均达成值为0.833，达到预设达标阈值0.60。低分段占比为0.0%，高分段占比为66.2%。</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -732,7 +732,7 @@
         <v>0.8156325275</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>课程目标3综合平均达成值为0.816，达到预设达标阈值0.70。低分段占比为1.2%，高分段占比为67.5%。</t>
+          <t>课程目标3综合平均达成值为0.816，达到预设达标阈值0.60。低分段占比为1.2%，高分段占比为67.5%。</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
